--- a/AAII_Financials/Yearly/OCLDY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OCLDY_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>

--- a/AAII_Financials/Yearly/OCLDY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OCLDY_YR_FIN.xlsx
@@ -711,10 +711,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5386900</v>
+        <v>5412500</v>
       </c>
       <c r="E8" s="3">
-        <v>5312900</v>
+        <v>5332200</v>
       </c>
       <c r="F8" s="3">
         <v>5127000</v>
@@ -771,10 +771,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2275700</v>
+        <v>2301300</v>
       </c>
       <c r="E10" s="3">
-        <v>2153000</v>
+        <v>2172200</v>
       </c>
       <c r="F10" s="3">
         <v>1828600</v>
@@ -976,10 +976,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>591600</v>
+        <v>617200</v>
       </c>
       <c r="E18" s="3">
-        <v>491400</v>
+        <v>510600</v>
       </c>
       <c r="F18" s="3">
         <v>430100</v>
@@ -1020,10 +1020,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>145200</v>
+        <v>170800</v>
       </c>
       <c r="E20" s="3">
-        <v>-35300</v>
+        <v>-16000</v>
       </c>
       <c r="F20" s="3">
         <v>-15500</v>
@@ -1380,10 +1380,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-145200</v>
+        <v>-170800</v>
       </c>
       <c r="E32" s="3">
-        <v>35300</v>
+        <v>16000</v>
       </c>
       <c r="F32" s="3">
         <v>15500</v>
